--- a/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.55</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.43</v>
@@ -3094,7 +3094,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.59</v>
@@ -5274,7 +5274,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR22" t="n">
         <v>1.82</v>
@@ -5492,7 +5492,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
         <v>1.89</v>
@@ -6579,7 +6579,7 @@
         <v>1.33</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.95</v>
@@ -7454,7 +7454,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR32" t="n">
         <v>1.92</v>
@@ -8541,7 +8541,7 @@
         <v>1.25</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.18</v>
@@ -8980,7 +8980,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR39" t="n">
         <v>1.36</v>
@@ -10503,10 +10503,10 @@
         <v>0.8</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR46" t="n">
         <v>1.85</v>
@@ -11593,7 +11593,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.33</v>
@@ -12247,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.3</v>
@@ -13340,7 +13340,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR59" t="n">
         <v>1.79</v>
@@ -14866,7 +14866,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR66" t="n">
         <v>1.66</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.43</v>
@@ -16825,7 +16825,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.04</v>
@@ -17482,7 +17482,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR78" t="n">
         <v>1.56</v>
@@ -18136,7 +18136,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR81" t="n">
         <v>1.3</v>
@@ -20967,7 +20967,7 @@
         <v>1.67</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.59</v>
@@ -21185,7 +21185,7 @@
         <v>1.67</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.09</v>
@@ -21406,7 +21406,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR96" t="n">
         <v>1.61</v>
@@ -21842,7 +21842,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR98" t="n">
         <v>1.66</v>
@@ -24237,7 +24237,7 @@
         <v>1.58</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.3</v>
@@ -24673,7 +24673,7 @@
         <v>2.18</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.76</v>
@@ -25330,7 +25330,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR114" t="n">
         <v>1.52</v>
@@ -25763,7 +25763,7 @@
         <v>1.15</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.18</v>
@@ -27510,7 +27510,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR124" t="n">
         <v>1.45</v>
@@ -28161,7 +28161,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.26</v>
@@ -29469,7 +29469,7 @@
         <v>1.86</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.5</v>
@@ -31216,7 +31216,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR141" t="n">
         <v>1.66</v>
@@ -31867,7 +31867,7 @@
         <v>1.25</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.35</v>
@@ -33178,7 +33178,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR150" t="n">
         <v>1.64</v>
@@ -34704,7 +34704,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR157" t="n">
         <v>1.57</v>
@@ -35794,7 +35794,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR162" t="n">
         <v>1.46</v>
@@ -36009,7 +36009,7 @@
         <v>1.18</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.26</v>
@@ -38625,7 +38625,7 @@
         <v>1.37</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.59</v>
@@ -39279,7 +39279,7 @@
         <v>1.05</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.04</v>
@@ -39933,7 +39933,7 @@
         <v>1</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AQ181" t="n">
         <v>1.09</v>
@@ -41462,7 +41462,7 @@
         <v>0.95</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR188" t="n">
         <v>1.48</v>
@@ -42331,7 +42331,7 @@
         <v>1.19</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.35</v>
@@ -42770,7 +42770,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AR194" t="n">
         <v>1.2</v>
@@ -44372,6 +44372,224 @@
       </c>
       <c r="BP201" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>8231529</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>46081.67708333334</v>
+      </c>
+      <c r="F202" t="n">
+        <v>23</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>GKS Katowice</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Górnik Zabrze</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="n">
+        <v>2</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="n">
+        <v>1</v>
+      </c>
+      <c r="N202" t="n">
+        <v>4</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>['23', '85', '90+7']</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S202" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U202" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V202" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X202" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
@@ -44099,13 +44099,13 @@
         <v>6</v>
       </c>
       <c r="AX200" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY200" t="n">
         <v>9</v>
       </c>
       <c r="AZ200" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA200" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.43</v>
@@ -1350,7 +1350,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.3</v>
@@ -1786,7 +1786,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.35</v>
@@ -2658,7 +2658,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR10" t="n">
         <v>0.9</v>
@@ -2876,7 +2876,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR11" t="n">
         <v>1.21</v>
@@ -3530,7 +3530,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR14" t="n">
         <v>1.74</v>
@@ -3745,10 +3745,10 @@
         <v>3</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR15" t="n">
         <v>2.02</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.04</v>
@@ -4402,7 +4402,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR18" t="n">
         <v>0.5600000000000001</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.3</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.26</v>
@@ -5053,7 +5053,7 @@
         <v>1.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.35</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.48</v>
@@ -5925,10 +5925,10 @@
         <v>1.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR25" t="n">
         <v>1.73</v>
@@ -6364,7 +6364,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR27" t="n">
         <v>1.49</v>
@@ -6582,7 +6582,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR28" t="n">
         <v>1.57</v>
@@ -7018,7 +7018,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR30" t="n">
         <v>1.88</v>
@@ -7233,7 +7233,7 @@
         <v>2.33</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.43</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.43</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.3</v>
@@ -9195,10 +9195,10 @@
         <v>2</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR40" t="n">
         <v>1.44</v>
@@ -9413,7 +9413,7 @@
         <v>2.33</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.09</v>
@@ -9631,10 +9631,10 @@
         <v>1</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR42" t="n">
         <v>1.52</v>
@@ -9849,10 +9849,10 @@
         <v>1.4</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR43" t="n">
         <v>1.44</v>
@@ -11157,10 +11157,10 @@
         <v>1.25</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR49" t="n">
         <v>1.4</v>
@@ -11378,7 +11378,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR50" t="n">
         <v>1.13</v>
@@ -11596,7 +11596,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR51" t="n">
         <v>1.29</v>
@@ -11811,7 +11811,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.3</v>
@@ -12029,7 +12029,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.26</v>
@@ -12465,7 +12465,7 @@
         <v>0.83</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.43</v>
@@ -12683,7 +12683,7 @@
         <v>1.17</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.04</v>
@@ -12904,7 +12904,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR57" t="n">
         <v>1.32</v>
@@ -13555,10 +13555,10 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR60" t="n">
         <v>1.67</v>
@@ -13994,7 +13994,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR62" t="n">
         <v>1.32</v>
@@ -14212,7 +14212,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR63" t="n">
         <v>1.76</v>
@@ -14430,7 +14430,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR64" t="n">
         <v>1.84</v>
@@ -14863,7 +14863,7 @@
         <v>1.71</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.48</v>
@@ -15299,10 +15299,10 @@
         <v>2.17</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR68" t="n">
         <v>1.52</v>
@@ -15517,7 +15517,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.26</v>
@@ -15953,10 +15953,10 @@
         <v>1.67</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR71" t="n">
         <v>1.43</v>
@@ -16171,7 +16171,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.09</v>
@@ -16389,7 +16389,7 @@
         <v>1.29</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.3</v>
@@ -17043,10 +17043,10 @@
         <v>1.86</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR76" t="n">
         <v>1.46</v>
@@ -17264,7 +17264,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR77" t="n">
         <v>1.79</v>
@@ -17479,7 +17479,7 @@
         <v>0.78</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.36</v>
@@ -17918,7 +17918,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR80" t="n">
         <v>1.34</v>
@@ -18354,7 +18354,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR82" t="n">
         <v>1.73</v>
@@ -18569,10 +18569,10 @@
         <v>2.13</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR83" t="n">
         <v>1.81</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.18</v>
@@ -19226,7 +19226,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR86" t="n">
         <v>1.73</v>
@@ -19444,7 +19444,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR87" t="n">
         <v>1.67</v>
@@ -19877,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.04</v>
@@ -20095,10 +20095,10 @@
         <v>1.44</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR90" t="n">
         <v>1.57</v>
@@ -20531,7 +20531,7 @@
         <v>1.8</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.3</v>
@@ -20749,7 +20749,7 @@
         <v>1.22</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.3</v>
@@ -20970,7 +20970,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR94" t="n">
         <v>1.54</v>
@@ -21624,7 +21624,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR97" t="n">
         <v>1.64</v>
@@ -22057,7 +22057,7 @@
         <v>1.09</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.18</v>
@@ -22278,7 +22278,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR100" t="n">
         <v>1.33</v>
@@ -22711,7 +22711,7 @@
         <v>1.18</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.35</v>
@@ -22929,7 +22929,7 @@
         <v>1.5</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.09</v>
@@ -23147,10 +23147,10 @@
         <v>0.82</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR104" t="n">
         <v>1.45</v>
@@ -23365,10 +23365,10 @@
         <v>1.45</v>
       </c>
       <c r="AP105" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR105" t="n">
         <v>1.5</v>
@@ -24455,7 +24455,7 @@
         <v>1.25</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.43</v>
@@ -24676,7 +24676,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR111" t="n">
         <v>1.82</v>
@@ -24894,7 +24894,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR112" t="n">
         <v>1.8</v>
@@ -25109,10 +25109,10 @@
         <v>1.91</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR113" t="n">
         <v>1.63</v>
@@ -25327,7 +25327,7 @@
         <v>1.08</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.36</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.3</v>
@@ -26199,10 +26199,10 @@
         <v>1.42</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR118" t="n">
         <v>1.64</v>
@@ -26635,7 +26635,7 @@
         <v>1.31</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.35</v>
@@ -26856,7 +26856,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR121" t="n">
         <v>1.6</v>
@@ -27074,7 +27074,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR122" t="n">
         <v>1.44</v>
@@ -27289,7 +27289,7 @@
         <v>1.69</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.43</v>
@@ -27507,7 +27507,7 @@
         <v>2.07</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.48</v>
@@ -27946,7 +27946,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR126" t="n">
         <v>1.58</v>
@@ -28382,7 +28382,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR128" t="n">
         <v>1.79</v>
@@ -28600,7 +28600,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR129" t="n">
         <v>1.69</v>
@@ -28818,7 +28818,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR130" t="n">
         <v>1.67</v>
@@ -29036,7 +29036,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR131" t="n">
         <v>1.14</v>
@@ -29251,7 +29251,7 @@
         <v>1.2</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.18</v>
@@ -29472,7 +29472,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR133" t="n">
         <v>1.95</v>
@@ -29905,7 +29905,7 @@
         <v>0.85</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.26</v>
@@ -30341,10 +30341,10 @@
         <v>1.47</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR137" t="n">
         <v>1.83</v>
@@ -30780,7 +30780,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR139" t="n">
         <v>1.79</v>
@@ -31213,7 +31213,7 @@
         <v>1.88</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.48</v>
@@ -31434,7 +31434,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR142" t="n">
         <v>1.61</v>
@@ -32088,7 +32088,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR145" t="n">
         <v>1.21</v>
@@ -32303,10 +32303,10 @@
         <v>1.93</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR146" t="n">
         <v>1.43</v>
@@ -32521,10 +32521,10 @@
         <v>1.6</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR147" t="n">
         <v>1.43</v>
@@ -32957,7 +32957,7 @@
         <v>1.56</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.43</v>
@@ -33614,7 +33614,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR152" t="n">
         <v>1.83</v>
@@ -33829,7 +33829,7 @@
         <v>1.18</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.04</v>
@@ -34265,10 +34265,10 @@
         <v>1.87</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR155" t="n">
         <v>1.49</v>
@@ -34486,7 +34486,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR156" t="n">
         <v>1.34</v>
@@ -34701,7 +34701,7 @@
         <v>1.25</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.36</v>
@@ -34922,7 +34922,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR158" t="n">
         <v>1.66</v>
@@ -35137,10 +35137,10 @@
         <v>1.47</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR159" t="n">
         <v>1.58</v>
@@ -35358,7 +35358,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR160" t="n">
         <v>1.52</v>
@@ -35791,7 +35791,7 @@
         <v>1.18</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.36</v>
@@ -36230,7 +36230,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR164" t="n">
         <v>1.58</v>
@@ -36445,7 +36445,7 @@
         <v>1.39</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.43</v>
@@ -36881,10 +36881,10 @@
         <v>1.61</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR167" t="n">
         <v>1.36</v>
@@ -37317,7 +37317,7 @@
         <v>1.5</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.43</v>
@@ -37538,7 +37538,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR170" t="n">
         <v>1.58</v>
@@ -37756,7 +37756,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR171" t="n">
         <v>1.66</v>
@@ -38407,7 +38407,7 @@
         <v>1.26</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.3</v>
@@ -38628,7 +38628,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR175" t="n">
         <v>1.89</v>
@@ -38846,7 +38846,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR176" t="n">
         <v>1.83</v>
@@ -39061,10 +39061,10 @@
         <v>1.44</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR177" t="n">
         <v>1.65</v>
@@ -39500,7 +39500,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR179" t="n">
         <v>1.58</v>
@@ -39715,7 +39715,7 @@
         <v>1.35</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.3</v>
@@ -40154,7 +40154,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR182" t="n">
         <v>1.4</v>
@@ -40369,10 +40369,10 @@
         <v>1.5</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR183" t="n">
         <v>1.43</v>
@@ -40587,7 +40587,7 @@
         <v>1</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.04</v>
@@ -41241,7 +41241,7 @@
         <v>1.3</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.26</v>
@@ -41459,7 +41459,7 @@
         <v>1.65</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.48</v>
@@ -42113,10 +42113,10 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AR191" t="n">
         <v>1.69</v>
@@ -42552,7 +42552,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR193" t="n">
         <v>1.77</v>
@@ -42985,10 +42985,10 @@
         <v>1.35</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR195" t="n">
         <v>1.78</v>
@@ -43206,7 +43206,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR196" t="n">
         <v>1.63</v>
@@ -43424,7 +43424,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AR197" t="n">
         <v>1.66</v>
@@ -44093,13 +44093,13 @@
         <v>3</v>
       </c>
       <c r="AV200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW200" t="n">
         <v>6</v>
       </c>
       <c r="AX200" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY200" t="n">
         <v>9</v>
@@ -44311,16 +44311,16 @@
         <v>4</v>
       </c>
       <c r="AV201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW201" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX201" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY201" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ201" t="n">
         <v>22</v>
@@ -44590,6 +44590,878 @@
       </c>
       <c r="BP202" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>8181620</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>46082.34375</v>
+      </c>
+      <c r="F203" t="n">
+        <v>23</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Nieciecza</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>1</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S203" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U203" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V203" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X203" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>8231588</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>46082.44791666666</v>
+      </c>
+      <c r="F204" t="n">
+        <v>23</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Jagiellonia Białystok</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Legia Warszawa</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>2</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="n">
+        <v>3</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="n">
+        <v>2</v>
+      </c>
+      <c r="N204" t="n">
+        <v>4</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>['17', '22']</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>['45+1', '56']</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S204" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X204" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>8181603</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>46082.5625</v>
+      </c>
+      <c r="F205" t="n">
+        <v>23</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Raków Częstochowa</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>2</v>
+      </c>
+      <c r="J205" t="n">
+        <v>2</v>
+      </c>
+      <c r="K205" t="n">
+        <v>4</v>
+      </c>
+      <c r="L205" t="n">
+        <v>4</v>
+      </c>
+      <c r="M205" t="n">
+        <v>3</v>
+      </c>
+      <c r="N205" t="n">
+        <v>7</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>['19', '45', '55', '90+1']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['8', '37', '73']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S205" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X205" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8181622</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>46083.625</v>
+      </c>
+      <c r="F206" t="n">
+        <v>23</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Zagłębie Lubin</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Wisła Płock</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>1</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1</v>
+      </c>
+      <c r="L206" t="n">
+        <v>2</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>2</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['14', '66']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>3</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S206" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V206" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X206" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
@@ -45398,7 +45398,7 @@
         <v>2.78</v>
       </c>
       <c r="AU206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV206" t="n">
         <v>4</v>
@@ -45407,13 +45407,13 @@
         <v>7</v>
       </c>
       <c r="AX206" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY206" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ206" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA206" t="n">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.35</v>
@@ -2873,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR11" t="n">
         <v>1.21</v>
@@ -5925,7 +5925,7 @@
         <v>1.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.48</v>
@@ -6146,7 +6146,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR26" t="n">
         <v>1.76</v>
@@ -6364,7 +6364,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR27" t="n">
         <v>1.49</v>
@@ -6797,7 +6797,7 @@
         <v>1.33</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.35</v>
@@ -8544,7 +8544,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR37" t="n">
         <v>1.35</v>
@@ -9195,7 +9195,7 @@
         <v>2</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.73</v>
@@ -9849,7 +9849,7 @@
         <v>1.4</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.96</v>
@@ -10942,7 +10942,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR48" t="n">
         <v>1.84</v>
@@ -11375,7 +11375,7 @@
         <v>2.67</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.43</v>
@@ -11596,7 +11596,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR51" t="n">
         <v>1.29</v>
@@ -14430,7 +14430,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR64" t="n">
         <v>1.84</v>
@@ -14648,7 +14648,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR65" t="n">
         <v>1.77</v>
@@ -15517,7 +15517,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.26</v>
@@ -15735,7 +15735,7 @@
         <v>1.75</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.3</v>
@@ -19008,7 +19008,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR85" t="n">
         <v>1.33</v>
@@ -19226,7 +19226,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR86" t="n">
         <v>1.73</v>
@@ -20095,7 +20095,7 @@
         <v>1.44</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.65</v>
@@ -20313,7 +20313,7 @@
         <v>2</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.43</v>
@@ -21624,7 +21624,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR97" t="n">
         <v>1.64</v>
@@ -22060,7 +22060,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR99" t="n">
         <v>1.6</v>
@@ -23801,7 +23801,7 @@
         <v>0.7</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.26</v>
@@ -25109,7 +25109,7 @@
         <v>1.91</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.43</v>
@@ -25766,7 +25766,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR116" t="n">
         <v>1.86</v>
@@ -26856,7 +26856,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR121" t="n">
         <v>1.6</v>
@@ -27289,7 +27289,7 @@
         <v>1.69</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.43</v>
@@ -29033,7 +29033,7 @@
         <v>1.62</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.65</v>
@@ -29254,7 +29254,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR132" t="n">
         <v>1.57</v>
@@ -30344,7 +30344,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR137" t="n">
         <v>1.83</v>
@@ -31213,7 +31213,7 @@
         <v>1.88</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.48</v>
@@ -32085,7 +32085,7 @@
         <v>1.53</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.48</v>
@@ -33393,7 +33393,7 @@
         <v>1.25</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.3</v>
@@ -33614,7 +33614,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR152" t="n">
         <v>1.83</v>
@@ -38189,7 +38189,7 @@
         <v>1</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.09</v>
@@ -39064,7 +39064,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR177" t="n">
         <v>1.65</v>
@@ -39715,7 +39715,7 @@
         <v>1.35</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.3</v>
@@ -41026,7 +41026,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AR186" t="n">
         <v>1.83</v>
@@ -42767,7 +42767,7 @@
         <v>1.35</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.36</v>
@@ -42988,7 +42988,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR195" t="n">
         <v>1.78</v>
@@ -43857,7 +43857,7 @@
         <v>1.45</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.43</v>
@@ -44732,7 +44732,7 @@
         <v>0.96</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AR203" t="n">
         <v>1.5</v>
@@ -45462,6 +45462,224 @@
       </c>
       <c r="BP206" t="n">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>8231636</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>46086.6875</v>
+      </c>
+      <c r="F207" t="n">
+        <v>19</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>2</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>2</v>
+      </c>
+      <c r="L207" t="n">
+        <v>3</v>
+      </c>
+      <c r="M207" t="n">
+        <v>1</v>
+      </c>
+      <c r="N207" t="n">
+        <v>4</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>['6', '8', '77']</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R207" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S207" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V207" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X207" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR10" t="n">
         <v>0.9</v>
@@ -3091,7 +3091,7 @@
         <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.48</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.65</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.04</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.09</v>
@@ -4402,7 +4402,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR18" t="n">
         <v>0.5600000000000001</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR19" t="n">
         <v>1.58</v>
@@ -4838,7 +4838,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR20" t="n">
         <v>1.89</v>
@@ -5053,7 +5053,7 @@
         <v>1.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.35</v>
@@ -5710,7 +5710,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR24" t="n">
         <v>1.2</v>
@@ -6361,7 +6361,7 @@
         <v>2.33</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.39</v>
@@ -6582,7 +6582,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR28" t="n">
         <v>1.57</v>
@@ -7233,7 +7233,7 @@
         <v>2.33</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.43</v>
@@ -7669,7 +7669,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.3</v>
@@ -7887,10 +7887,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR34" t="n">
         <v>1.42</v>
@@ -8326,7 +8326,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR36" t="n">
         <v>2.02</v>
@@ -8762,7 +8762,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR38" t="n">
         <v>1.75</v>
@@ -9198,7 +9198,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR40" t="n">
         <v>1.44</v>
@@ -9631,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.48</v>
@@ -9852,7 +9852,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR43" t="n">
         <v>1.44</v>
@@ -10285,7 +10285,7 @@
         <v>1.25</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.3</v>
@@ -10721,7 +10721,7 @@
         <v>2</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.43</v>
@@ -10939,7 +10939,7 @@
         <v>1</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.13</v>
@@ -11160,7 +11160,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR49" t="n">
         <v>1.4</v>
@@ -11811,10 +11811,10 @@
         <v>1.33</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR52" t="n">
         <v>1.48</v>
@@ -12029,10 +12029,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR53" t="n">
         <v>1.3</v>
@@ -12465,10 +12465,10 @@
         <v>0.83</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
         <v>1.8</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.36</v>
@@ -13558,7 +13558,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR60" t="n">
         <v>1.67</v>
@@ -13773,7 +13773,7 @@
         <v>1.43</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.35</v>
@@ -13991,10 +13991,10 @@
         <v>2.4</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR62" t="n">
         <v>1.32</v>
@@ -14212,7 +14212,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR63" t="n">
         <v>1.76</v>
@@ -15302,7 +15302,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR68" t="n">
         <v>1.52</v>
@@ -15520,7 +15520,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR69" t="n">
         <v>1.48</v>
@@ -15738,7 +15738,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR70" t="n">
         <v>1.18</v>
@@ -15953,7 +15953,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.65</v>
@@ -16389,7 +16389,7 @@
         <v>1.29</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.3</v>
@@ -16610,7 +16610,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR74" t="n">
         <v>1.41</v>
@@ -17264,7 +17264,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR77" t="n">
         <v>1.79</v>
@@ -17697,10 +17697,10 @@
         <v>1.22</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR79" t="n">
         <v>1.68</v>
@@ -17915,10 +17915,10 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR80" t="n">
         <v>1.34</v>
@@ -18572,7 +18572,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR83" t="n">
         <v>1.81</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.13</v>
@@ -19441,7 +19441,7 @@
         <v>1.89</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.43</v>
@@ -19662,7 +19662,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR88" t="n">
         <v>1.45</v>
@@ -19877,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.04</v>
@@ -20098,7 +20098,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR90" t="n">
         <v>1.57</v>
@@ -20531,10 +20531,10 @@
         <v>1.8</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR92" t="n">
         <v>1.56</v>
@@ -21839,7 +21839,7 @@
         <v>2</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.48</v>
@@ -22057,7 +22057,7 @@
         <v>1.09</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.13</v>
@@ -22493,10 +22493,10 @@
         <v>1.09</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR101" t="n">
         <v>1.39</v>
@@ -22929,7 +22929,7 @@
         <v>1.5</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.09</v>
@@ -23150,7 +23150,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR104" t="n">
         <v>1.45</v>
@@ -23365,10 +23365,10 @@
         <v>1.45</v>
       </c>
       <c r="AP105" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR105" t="n">
         <v>1.5</v>
@@ -23804,7 +23804,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR107" t="n">
         <v>1.17</v>
@@ -24240,7 +24240,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR109" t="n">
         <v>1.55</v>
@@ -24458,7 +24458,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR110" t="n">
         <v>1.64</v>
@@ -24676,7 +24676,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR111" t="n">
         <v>1.82</v>
@@ -25327,7 +25327,7 @@
         <v>1.08</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.36</v>
@@ -25545,10 +25545,10 @@
         <v>1.46</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR115" t="n">
         <v>1.55</v>
@@ -26199,7 +26199,7 @@
         <v>1.42</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.48</v>
@@ -26853,7 +26853,7 @@
         <v>1.23</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.39</v>
@@ -27074,7 +27074,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR122" t="n">
         <v>1.44</v>
@@ -27507,7 +27507,7 @@
         <v>2.07</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.48</v>
@@ -27725,7 +27725,7 @@
         <v>1.21</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.04</v>
@@ -28164,7 +28164,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR127" t="n">
         <v>1.55</v>
@@ -28382,7 +28382,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR128" t="n">
         <v>1.79</v>
@@ -28597,7 +28597,7 @@
         <v>1.54</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.48</v>
@@ -28818,7 +28818,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR130" t="n">
         <v>1.67</v>
@@ -29251,7 +29251,7 @@
         <v>1.2</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.13</v>
@@ -29908,7 +29908,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR135" t="n">
         <v>1.55</v>
@@ -30126,7 +30126,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR136" t="n">
         <v>1.86</v>
@@ -30562,7 +30562,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR138" t="n">
         <v>1.56</v>
@@ -30780,7 +30780,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR139" t="n">
         <v>1.79</v>
@@ -30995,7 +30995,7 @@
         <v>1.06</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.04</v>
@@ -31431,10 +31431,10 @@
         <v>1</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR142" t="n">
         <v>1.61</v>
@@ -31649,7 +31649,7 @@
         <v>1.47</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.43</v>
@@ -32303,10 +32303,10 @@
         <v>1.93</v>
       </c>
       <c r="AP146" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ146" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AQ146" t="n">
-        <v>1.73</v>
       </c>
       <c r="AR146" t="n">
         <v>1.43</v>
@@ -33175,7 +33175,7 @@
         <v>1.76</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.48</v>
@@ -33829,7 +33829,7 @@
         <v>1.18</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.04</v>
@@ -34047,7 +34047,7 @@
         <v>1.19</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.09</v>
@@ -34265,10 +34265,10 @@
         <v>1.87</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR155" t="n">
         <v>1.49</v>
@@ -34919,7 +34919,7 @@
         <v>1.71</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.43</v>
@@ -35140,7 +35140,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR159" t="n">
         <v>1.58</v>
@@ -35358,7 +35358,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR160" t="n">
         <v>1.52</v>
@@ -35576,7 +35576,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR161" t="n">
         <v>1.84</v>
@@ -35791,7 +35791,7 @@
         <v>1.18</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.36</v>
@@ -36012,7 +36012,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR163" t="n">
         <v>1.87</v>
@@ -36230,7 +36230,7 @@
         <v>1.04</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR164" t="n">
         <v>1.58</v>
@@ -36448,7 +36448,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR165" t="n">
         <v>1.82</v>
@@ -37102,7 +37102,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR168" t="n">
         <v>1.8</v>
@@ -37317,7 +37317,7 @@
         <v>1.5</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.43</v>
@@ -37535,7 +37535,7 @@
         <v>1.44</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.65</v>
@@ -37753,10 +37753,10 @@
         <v>1.47</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR171" t="n">
         <v>1.66</v>
@@ -37971,7 +37971,7 @@
         <v>1.58</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.43</v>
@@ -38407,7 +38407,7 @@
         <v>1.26</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.3</v>
@@ -38846,7 +38846,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR176" t="n">
         <v>1.83</v>
@@ -39497,7 +39497,7 @@
         <v>1.74</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.43</v>
@@ -39718,7 +39718,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR180" t="n">
         <v>1.64</v>
@@ -40154,7 +40154,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AR182" t="n">
         <v>1.4</v>
@@ -40369,7 +40369,7 @@
         <v>1.5</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.48</v>
@@ -40808,7 +40808,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR185" t="n">
         <v>1.5</v>
@@ -41244,7 +41244,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR187" t="n">
         <v>1.88</v>
@@ -41459,7 +41459,7 @@
         <v>1.65</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.48</v>
@@ -41677,7 +41677,7 @@
         <v>1.14</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.3</v>
@@ -42116,7 +42116,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AR191" t="n">
         <v>1.69</v>
@@ -42985,7 +42985,7 @@
         <v>1.35</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.39</v>
@@ -43203,7 +43203,7 @@
         <v>1.52</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.65</v>
@@ -43421,10 +43421,10 @@
         <v>1.52</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR197" t="n">
         <v>1.66</v>
@@ -43642,7 +43642,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AR198" t="n">
         <v>1.37</v>
@@ -43860,7 +43860,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR199" t="n">
         <v>1.22</v>
@@ -44296,7 +44296,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AR201" t="n">
         <v>1.47</v>
@@ -44729,7 +44729,7 @@
         <v>1.33</v>
       </c>
       <c r="AP203" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.39</v>
@@ -44947,7 +44947,7 @@
         <v>1.09</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.09</v>
@@ -45383,7 +45383,7 @@
         <v>1.5</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.43</v>
@@ -45680,6 +45680,660 @@
       </c>
       <c r="BP207" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>8231500</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>46087.6875</v>
+      </c>
+      <c r="F208" t="n">
+        <v>24</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Lechia Gdańsk</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Jagiellonia Białystok</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>3</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['43', '81', '90+4']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R208" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S208" t="n">
+        <v>3</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U208" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V208" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X208" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8231499</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>46088.44791666666</v>
+      </c>
+      <c r="F209" t="n">
+        <v>24</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Korona Kielce</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Nieciecza</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>1</v>
+      </c>
+      <c r="L209" t="n">
+        <v>2</v>
+      </c>
+      <c r="M209" t="n">
+        <v>1</v>
+      </c>
+      <c r="N209" t="n">
+        <v>3</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>['43', '52']</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R209" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S209" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U209" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V209" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W209" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X209" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>8231530</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>46088.5625</v>
+      </c>
+      <c r="F210" t="n">
+        <v>24</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Piast Gliwice</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Zagłębie Lubin</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="n">
+        <v>2</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>3</v>
+      </c>
+      <c r="N210" t="n">
+        <v>4</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>['27', '69', '89']</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R210" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S210" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V210" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X210" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Poland Ekstraklasa_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.43</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.71</v>
@@ -3530,7 +3530,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR14" t="n">
         <v>1.74</v>
@@ -3966,7 +3966,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR16" t="n">
         <v>1.7</v>
@@ -5271,7 +5271,7 @@
         <v>0.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.36</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.48</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.43</v>
@@ -8108,7 +8108,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR35" t="n">
         <v>1.5</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.38</v>
@@ -10067,7 +10067,7 @@
         <v>0.8</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.35</v>
@@ -12683,10 +12683,10 @@
         <v>1.17</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR56" t="n">
         <v>1.75</v>
@@ -13555,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.71</v>
@@ -14645,7 +14645,7 @@
         <v>1.14</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.13</v>
@@ -15956,7 +15956,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR71" t="n">
         <v>1.43</v>
@@ -16828,7 +16828,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR75" t="n">
         <v>1.94</v>
@@ -17046,7 +17046,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR76" t="n">
         <v>1.46</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.48</v>
@@ -18569,7 +18569,7 @@
         <v>2.13</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.65</v>
@@ -19880,7 +19880,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR89" t="n">
         <v>1.55</v>
@@ -20970,7 +20970,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR94" t="n">
         <v>1.54</v>
@@ -21621,7 +21621,7 @@
         <v>1.36</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.39</v>
@@ -22711,7 +22711,7 @@
         <v>1.18</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.35</v>
@@ -23586,7 +23586,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR106" t="n">
         <v>1.65</v>
@@ -24894,7 +24894,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR112" t="n">
         <v>1.8</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.3</v>
@@ -26417,7 +26417,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.09</v>
@@ -27728,7 +27728,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR125" t="n">
         <v>1.6</v>
@@ -29036,7 +29036,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR131" t="n">
         <v>1.14</v>
@@ -30341,7 +30341,7 @@
         <v>1.47</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.39</v>
@@ -30559,7 +30559,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.38</v>
@@ -30998,7 +30998,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR140" t="n">
         <v>1.57</v>
@@ -32524,7 +32524,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR147" t="n">
         <v>1.43</v>
@@ -33832,7 +33832,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR153" t="n">
         <v>1.42</v>
@@ -34486,7 +34486,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR156" t="n">
         <v>1.34</v>
@@ -36227,7 +36227,7 @@
         <v>1.71</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.65</v>
@@ -36445,7 +36445,7 @@
         <v>1.39</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.5</v>
@@ -37538,7 +37538,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR170" t="n">
         <v>1.58</v>
@@ -38628,7 +38628,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR175" t="n">
         <v>1.89</v>
@@ -39282,7 +39282,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR178" t="n">
         <v>1.51</v>
@@ -40590,7 +40590,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR184" t="n">
         <v>1.35</v>
@@ -41241,7 +41241,7 @@
         <v>1.3</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.21</v>
@@ -41895,7 +41895,7 @@
         <v>1.52</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.43</v>
@@ -43206,7 +43206,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR196" t="n">
         <v>1.63</v>
@@ -44078,7 +44078,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AR200" t="n">
         <v>1.79</v>
@@ -45165,7 +45165,7 @@
         <v>1.55</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.48</v>
@@ -46061,13 +46061,13 @@
         <v>6</v>
       </c>
       <c r="AX209" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY209" t="n">
         <v>10</v>
       </c>
       <c r="AZ209" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA209" t="n">
         <v>5</v>
@@ -46334,6 +46334,224 @@
       </c>
       <c r="BP210" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8231502</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>46088.67708333334</v>
+      </c>
+      <c r="F211" t="n">
+        <v>24</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Widzew Łódź</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Lech Poznań</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>2</v>
+      </c>
+      <c r="L211" t="n">
+        <v>2</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>3</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['34', '52']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S211" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U211" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X211" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
